--- a/notebooks/Random Forest/opj_predictions_2019_comparison.xlsx
+++ b/notebooks/Random Forest/opj_predictions_2019_comparison.xlsx
@@ -492,16 +492,16 @@
         <v>2019</v>
       </c>
       <c r="C3" t="n">
-        <v>69.06955142322956</v>
+        <v>69.06955142322958</v>
       </c>
       <c r="D3" t="n">
         <v>68.42</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6495514232295534</v>
+        <v>-0.6495514232295818</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.9493589933200137</v>
+        <v>-0.9493589933200551</v>
       </c>
     </row>
     <row r="4">
@@ -514,16 +514,16 @@
         <v>2019</v>
       </c>
       <c r="C4" t="n">
-        <v>71.62213742022359</v>
+        <v>71.62213742022357</v>
       </c>
       <c r="D4" t="n">
         <v>71.56</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0621374202235927</v>
+        <v>-0.06213742022356428</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08683261629903954</v>
+        <v>-0.08683261629899983</v>
       </c>
     </row>
     <row r="5">
@@ -580,16 +580,16 @@
         <v>2019</v>
       </c>
       <c r="C7" t="n">
-        <v>71.80376797842979</v>
+        <v>71.80376797842976</v>
       </c>
       <c r="D7" t="n">
         <v>72.14</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3362320215702113</v>
+        <v>0.3362320215702397</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4660826470338387</v>
+        <v>0.4660826470338781</v>
       </c>
     </row>
     <row r="8">
@@ -624,16 +624,16 @@
         <v>2019</v>
       </c>
       <c r="C9" t="n">
-        <v>73.67431899905648</v>
+        <v>73.6743189990565</v>
       </c>
       <c r="D9" t="n">
         <v>74.11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4356810009435179</v>
+        <v>0.4356810009435037</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5878842274234488</v>
+        <v>0.5878842274234296</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         <v>2019</v>
       </c>
       <c r="C10" t="n">
-        <v>71.64284069604395</v>
+        <v>71.64284069604392</v>
       </c>
       <c r="D10" t="n">
         <v>71.78</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1371593039560537</v>
+        <v>0.1371593039560821</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1910828976818803</v>
+        <v>0.1910828976819199</v>
       </c>
     </row>
     <row r="11">
@@ -734,16 +734,16 @@
         <v>2019</v>
       </c>
       <c r="C14" t="n">
-        <v>71.10875959054833</v>
+        <v>71.10875959054832</v>
       </c>
       <c r="D14" t="n">
         <v>71.41</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3012404094516654</v>
+        <v>0.3012404094516796</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4218462532581787</v>
+        <v>0.4218462532581986</v>
       </c>
     </row>
     <row r="15">
@@ -778,16 +778,16 @@
         <v>2019</v>
       </c>
       <c r="C16" t="n">
-        <v>76.27844989538239</v>
+        <v>76.27844989538235</v>
       </c>
       <c r="D16" t="n">
         <v>76.2</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.07844989538239133</v>
+        <v>-0.0784498953823487</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1029526186120621</v>
+        <v>-0.1029526186120062</v>
       </c>
     </row>
     <row r="17">
@@ -844,16 +844,16 @@
         <v>2019</v>
       </c>
       <c r="C19" t="n">
-        <v>69.81525128851143</v>
+        <v>69.81525128851145</v>
       </c>
       <c r="D19" t="n">
         <v>69.91</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09474871148856323</v>
+        <v>0.09474871148854902</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1355295544107613</v>
+        <v>0.135529554410741</v>
       </c>
     </row>
     <row r="20">
@@ -866,16 +866,16 @@
         <v>2019</v>
       </c>
       <c r="C20" t="n">
-        <v>75.96998255952388</v>
+        <v>75.96998255952386</v>
       </c>
       <c r="D20" t="n">
         <v>75.7</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2699825595238821</v>
+        <v>-0.2699825595238536</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3566480310751414</v>
+        <v>-0.3566480310751038</v>
       </c>
     </row>
     <row r="21">
@@ -910,16 +910,16 @@
         <v>2019</v>
       </c>
       <c r="C22" t="n">
-        <v>72.28120728076274</v>
+        <v>72.28120728076276</v>
       </c>
       <c r="D22" t="n">
         <v>72.48</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1987927192372609</v>
+        <v>0.1987927192372467</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2742725155039472</v>
+        <v>0.2742725155039276</v>
       </c>
     </row>
     <row r="23">
@@ -954,16 +954,16 @@
         <v>2019</v>
       </c>
       <c r="C24" t="n">
-        <v>74.65252651556783</v>
+        <v>74.65252651556784</v>
       </c>
       <c r="D24" t="n">
         <v>74.05</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6025265155678312</v>
+        <v>-0.6025265155678454</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8136752404697248</v>
+        <v>-0.8136752404697439</v>
       </c>
     </row>
     <row r="25">
@@ -998,16 +998,16 @@
         <v>2019</v>
       </c>
       <c r="C26" t="n">
-        <v>70.59115411079668</v>
+        <v>70.59115411079667</v>
       </c>
       <c r="D26" t="n">
         <v>70.75</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1588458892033202</v>
+        <v>0.1588458892033344</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2245171578845515</v>
+        <v>0.2245171578845716</v>
       </c>
     </row>
     <row r="27">
@@ -1064,16 +1064,16 @@
         <v>2019</v>
       </c>
       <c r="C29" t="n">
-        <v>72.9509510104928</v>
+        <v>72.95095101049279</v>
       </c>
       <c r="D29" t="n">
         <v>73.38</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4290489895071943</v>
+        <v>0.4290489895072085</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5846947254118211</v>
+        <v>0.5846947254118404</v>
       </c>
     </row>
     <row r="30">
@@ -1108,16 +1108,16 @@
         <v>2019</v>
       </c>
       <c r="C31" t="n">
-        <v>74.51365689074809</v>
+        <v>74.51365689074814</v>
       </c>
       <c r="D31" t="n">
         <v>74.67</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1563431092519068</v>
+        <v>0.1563431092518641</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2093787454826661</v>
+        <v>0.209378745482609</v>
       </c>
     </row>
     <row r="32">
@@ -1130,16 +1130,16 @@
         <v>2019</v>
       </c>
       <c r="C32" t="n">
-        <v>71.22030681063455</v>
+        <v>71.22030681063457</v>
       </c>
       <c r="D32" t="n">
         <v>71.04000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1803068106345478</v>
+        <v>-0.180306810634562</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.2538102627175504</v>
+        <v>-0.2538102627175703</v>
       </c>
     </row>
     <row r="33">
@@ -1152,16 +1152,16 @@
         <v>2019</v>
       </c>
       <c r="C33" t="n">
-        <v>71.62940846649093</v>
+        <v>71.6294084664909</v>
       </c>
       <c r="D33" t="n">
         <v>72.55</v>
       </c>
       <c r="E33" t="n">
-        <v>0.920591533509068</v>
+        <v>0.9205915335090964</v>
       </c>
       <c r="F33" t="n">
-        <v>1.268906317724422</v>
+        <v>1.268906317724461</v>
       </c>
     </row>
     <row r="34">
@@ -1174,16 +1174,16 @@
         <v>2019</v>
       </c>
       <c r="C34" t="n">
-        <v>71.72408277879006</v>
+        <v>71.72408277879003</v>
       </c>
       <c r="D34" t="n">
         <v>72.19</v>
       </c>
       <c r="E34" t="n">
-        <v>0.465917221209935</v>
+        <v>0.4659172212099634</v>
       </c>
       <c r="F34" t="n">
-        <v>0.6454041019669413</v>
+        <v>0.6454041019669807</v>
       </c>
     </row>
     <row r="35">
@@ -1196,16 +1196,16 @@
         <v>2019</v>
       </c>
       <c r="C35" t="n">
-        <v>70.32728960417653</v>
+        <v>70.3272896041765</v>
       </c>
       <c r="D35" t="n">
         <v>70.33</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002710395823470435</v>
+        <v>0.002710395823498857</v>
       </c>
       <c r="F35" t="n">
-        <v>0.003853825996687666</v>
+        <v>0.003853825996728077</v>
       </c>
     </row>
     <row r="36">
@@ -1218,16 +1218,16 @@
         <v>2019</v>
       </c>
       <c r="C36" t="n">
-        <v>72.15474508119409</v>
+        <v>72.15474508119406</v>
       </c>
       <c r="D36" t="n">
         <v>72.37</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2152549188059112</v>
+        <v>0.2152549188059396</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2974366710044372</v>
+        <v>0.2974366710044764</v>
       </c>
     </row>
     <row r="37">
@@ -1240,16 +1240,16 @@
         <v>2019</v>
       </c>
       <c r="C37" t="n">
-        <v>72.13424909817385</v>
+        <v>72.13424909817384</v>
       </c>
       <c r="D37" t="n">
         <v>72.29000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1557509018261527</v>
+        <v>0.1557509018261669</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2154529005756712</v>
+        <v>0.2154529005756908</v>
       </c>
     </row>
     <row r="38">
@@ -1262,16 +1262,16 @@
         <v>2019</v>
       </c>
       <c r="C38" t="n">
-        <v>71.48721326702741</v>
+        <v>71.48721326702736</v>
       </c>
       <c r="D38" t="n">
         <v>71.81</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3227867329725882</v>
+        <v>0.322786732972645</v>
       </c>
       <c r="F38" t="n">
-        <v>0.449501090339212</v>
+        <v>0.4495010903392913</v>
       </c>
     </row>
     <row r="39">
@@ -1284,16 +1284,16 @@
         <v>2019</v>
       </c>
       <c r="C39" t="n">
-        <v>71.78887683370436</v>
+        <v>71.78887683370435</v>
       </c>
       <c r="D39" t="n">
         <v>72.45999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6711231662956294</v>
+        <v>0.6711231662956436</v>
       </c>
       <c r="F39" t="n">
-        <v>0.9261981317908218</v>
+        <v>0.9261981317908414</v>
       </c>
     </row>
     <row r="40">
@@ -1306,16 +1306,16 @@
         <v>2019</v>
       </c>
       <c r="C40" t="n">
-        <v>73.07146062088241</v>
+        <v>73.07146062088238</v>
       </c>
       <c r="D40" t="n">
         <v>73.34999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2785393791175892</v>
+        <v>0.2785393791176176</v>
       </c>
       <c r="F40" t="n">
-        <v>0.3797401214963725</v>
+        <v>0.3797401214964112</v>
       </c>
     </row>
     <row r="41">
@@ -1328,16 +1328,16 @@
         <v>2019</v>
       </c>
       <c r="C41" t="n">
-        <v>70.79434511282517</v>
+        <v>70.79434511282518</v>
       </c>
       <c r="D41" t="n">
         <v>71.25</v>
       </c>
       <c r="E41" t="n">
-        <v>0.4556548871748305</v>
+        <v>0.4556548871748163</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6395156311225692</v>
+        <v>0.6395156311225492</v>
       </c>
     </row>
     <row r="42">
@@ -1372,16 +1372,16 @@
         <v>2019</v>
       </c>
       <c r="C43" t="n">
-        <v>70.29678067344616</v>
+        <v>70.29678067344615</v>
       </c>
       <c r="D43" t="n">
         <v>70.38</v>
       </c>
       <c r="E43" t="n">
-        <v>0.0832193265538308</v>
+        <v>0.08321932655384501</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1182428623953265</v>
+        <v>0.1182428623953467</v>
       </c>
     </row>
     <row r="44">
@@ -1416,16 +1416,16 @@
         <v>2019</v>
       </c>
       <c r="C45" t="n">
-        <v>70.45417915658439</v>
+        <v>70.4541791565844</v>
       </c>
       <c r="D45" t="n">
         <v>69.78</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.6741791565843869</v>
+        <v>-0.6741791565844011</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.9661495508518012</v>
+        <v>-0.9661495508518216</v>
       </c>
     </row>
     <row r="46">
@@ -1460,16 +1460,16 @@
         <v>2019</v>
       </c>
       <c r="C47" t="n">
-        <v>71.02327270019582</v>
+        <v>71.02327270019583</v>
       </c>
       <c r="D47" t="n">
         <v>70.70999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.3132727001958244</v>
+        <v>-0.3132727001958386</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.4430387501001619</v>
+        <v>-0.443038750100182</v>
       </c>
     </row>
     <row r="48">
@@ -1482,16 +1482,16 @@
         <v>2019</v>
       </c>
       <c r="C48" t="n">
-        <v>78.82082579365083</v>
+        <v>78.82082579365084</v>
       </c>
       <c r="D48" t="n">
         <v>79.03</v>
       </c>
       <c r="E48" t="n">
-        <v>0.2091742063491751</v>
+        <v>0.2091742063491608</v>
       </c>
       <c r="F48" t="n">
-        <v>0.2646769661510503</v>
+        <v>0.2646769661510323</v>
       </c>
     </row>
     <row r="49">
@@ -1548,16 +1548,16 @@
         <v>2019</v>
       </c>
       <c r="C51" t="n">
-        <v>69.92419964020129</v>
+        <v>69.92419964020131</v>
       </c>
       <c r="D51" t="n">
         <v>70.44</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5158003597987033</v>
+        <v>0.5158003597986891</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7322549116960582</v>
+        <v>0.732254911696038</v>
       </c>
     </row>
     <row r="52">
@@ -1570,16 +1570,16 @@
         <v>2019</v>
       </c>
       <c r="C52" t="n">
-        <v>70.73980761804654</v>
+        <v>70.73980761804657</v>
       </c>
       <c r="D52" t="n">
         <v>70.78</v>
       </c>
       <c r="E52" t="n">
-        <v>0.0401923819534602</v>
+        <v>0.04019238195343178</v>
       </c>
       <c r="F52" t="n">
-        <v>0.05678494200827945</v>
+        <v>0.0567849420082393</v>
       </c>
     </row>
     <row r="53">
@@ -1592,16 +1592,16 @@
         <v>2019</v>
       </c>
       <c r="C53" t="n">
-        <v>72.32680521552983</v>
+        <v>72.32680521552982</v>
       </c>
       <c r="D53" t="n">
         <v>72.73999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4131947844701642</v>
+        <v>0.4131947844701784</v>
       </c>
       <c r="F53" t="n">
-        <v>0.5680434210477925</v>
+        <v>0.568043421047812</v>
       </c>
     </row>
     <row r="54">
@@ -1614,16 +1614,16 @@
         <v>2019</v>
       </c>
       <c r="C54" t="n">
-        <v>72.18384325299365</v>
+        <v>72.18384325299367</v>
       </c>
       <c r="D54" t="n">
         <v>72.95</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7661567470063488</v>
+        <v>0.7661567470063346</v>
       </c>
       <c r="F54" t="n">
-        <v>1.050249139145098</v>
+        <v>1.050249139145078</v>
       </c>
     </row>
     <row r="55">
@@ -1658,16 +1658,16 @@
         <v>2019</v>
       </c>
       <c r="C56" t="n">
-        <v>69.15279908119655</v>
+        <v>69.15279908119658</v>
       </c>
       <c r="D56" t="n">
         <v>68.48999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.6627990811965532</v>
+        <v>-0.6627990811965816</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.96773117418098</v>
+        <v>-0.9677311741810215</v>
       </c>
     </row>
     <row r="57">
@@ -1702,16 +1702,16 @@
         <v>2019</v>
       </c>
       <c r="C58" t="n">
-        <v>74.97759795634921</v>
+        <v>74.97759795634924</v>
       </c>
       <c r="D58" t="n">
         <v>75.23999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>0.2624020436507806</v>
+        <v>0.2624020436507521</v>
       </c>
       <c r="F58" t="n">
-        <v>0.3487533807160826</v>
+        <v>0.3487533807160449</v>
       </c>
     </row>
     <row r="59">
@@ -1746,16 +1746,16 @@
         <v>2019</v>
       </c>
       <c r="C60" t="n">
-        <v>71.45719076675195</v>
+        <v>71.45719076675194</v>
       </c>
       <c r="D60" t="n">
         <v>71.09999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.3571907667519554</v>
+        <v>-0.3571907667519412</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.5023780123093606</v>
+        <v>-0.5023780123093406</v>
       </c>
     </row>
     <row r="61">
@@ -1790,16 +1790,16 @@
         <v>2019</v>
       </c>
       <c r="C62" t="n">
-        <v>73.00505463645018</v>
+        <v>73.00505463645017</v>
       </c>
       <c r="D62" t="n">
         <v>73.22</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2149453635498162</v>
+        <v>0.2149453635498304</v>
       </c>
       <c r="F62" t="n">
-        <v>0.2935609991120134</v>
+        <v>0.2935609991120328</v>
       </c>
     </row>
     <row r="63">
@@ -1812,16 +1812,16 @@
         <v>2019</v>
       </c>
       <c r="C63" t="n">
-        <v>72.6495272222222</v>
+        <v>72.64952722222219</v>
       </c>
       <c r="D63" t="n">
         <v>72.84</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1904727777777993</v>
+        <v>0.1904727777778135</v>
       </c>
       <c r="F63" t="n">
-        <v>0.2614947525779781</v>
+        <v>0.2614947525779976</v>
       </c>
     </row>
     <row r="64">
@@ -1834,16 +1834,16 @@
         <v>2019</v>
       </c>
       <c r="C64" t="n">
-        <v>73.511163252442</v>
+        <v>73.51116325244202</v>
       </c>
       <c r="D64" t="n">
         <v>73.28</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.231163252442002</v>
+        <v>-0.2311632524420162</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3154520366293695</v>
+        <v>-0.3154520366293889</v>
       </c>
     </row>
     <row r="65">
@@ -1856,16 +1856,16 @@
         <v>2019</v>
       </c>
       <c r="C65" t="n">
-        <v>70.27915689641972</v>
+        <v>70.27915689641971</v>
       </c>
       <c r="D65" t="n">
         <v>70.39</v>
       </c>
       <c r="E65" t="n">
-        <v>0.1108431035802795</v>
+        <v>0.1108431035802937</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1574699582046874</v>
+        <v>0.1574699582047076</v>
       </c>
     </row>
     <row r="66">
@@ -1878,16 +1878,16 @@
         <v>2019</v>
       </c>
       <c r="C66" t="n">
-        <v>71.48517254048733</v>
+        <v>71.48517254048734</v>
       </c>
       <c r="D66" t="n">
         <v>71.79000000000001</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3048274595126799</v>
+        <v>0.3048274595126657</v>
       </c>
       <c r="F66" t="n">
-        <v>0.4246099171370384</v>
+        <v>0.4246099171370186</v>
       </c>
     </row>
     <row r="67">
@@ -1922,16 +1922,16 @@
         <v>2019</v>
       </c>
       <c r="C68" t="n">
-        <v>74.49627790986789</v>
+        <v>74.4962779098679</v>
       </c>
       <c r="D68" t="n">
         <v>74.77</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2737220901321109</v>
+        <v>0.2737220901320967</v>
       </c>
       <c r="F68" t="n">
-        <v>0.3660854488860651</v>
+        <v>0.3660854488860462</v>
       </c>
     </row>
     <row r="69">
@@ -1944,16 +1944,16 @@
         <v>2019</v>
       </c>
       <c r="C69" t="n">
-        <v>72.99659633017313</v>
+        <v>72.99659633017312</v>
       </c>
       <c r="D69" t="n">
         <v>73.43000000000001</v>
       </c>
       <c r="E69" t="n">
-        <v>0.4334036698268733</v>
+        <v>0.4334036698268875</v>
       </c>
       <c r="F69" t="n">
-        <v>0.5902269778385854</v>
+        <v>0.5902269778386048</v>
       </c>
     </row>
     <row r="70">
@@ -2010,16 +2010,16 @@
         <v>2019</v>
       </c>
       <c r="C72" t="n">
-        <v>72.26169002159344</v>
+        <v>72.26169002159342</v>
       </c>
       <c r="D72" t="n">
         <v>72.58</v>
       </c>
       <c r="E72" t="n">
-        <v>0.3183099784065604</v>
+        <v>0.3183099784065746</v>
       </c>
       <c r="F72" t="n">
-        <v>0.4385643130429325</v>
+        <v>0.438564313042952</v>
       </c>
     </row>
     <row r="73">
@@ -2076,16 +2076,16 @@
         <v>2019</v>
       </c>
       <c r="C75" t="n">
-        <v>72.1624070999365</v>
+        <v>72.16240709993652</v>
       </c>
       <c r="D75" t="n">
         <v>72.76000000000001</v>
       </c>
       <c r="E75" t="n">
-        <v>0.5975929000635034</v>
+        <v>0.5975929000634892</v>
       </c>
       <c r="F75" t="n">
-        <v>0.8213206432978331</v>
+        <v>0.8213206432978135</v>
       </c>
     </row>
     <row r="76">
@@ -2120,16 +2120,16 @@
         <v>2019</v>
       </c>
       <c r="C77" t="n">
-        <v>74.84486142857146</v>
+        <v>74.84486142857148</v>
       </c>
       <c r="D77" t="n">
         <v>75.11</v>
       </c>
       <c r="E77" t="n">
-        <v>0.2651385714285368</v>
+        <v>0.2651385714285226</v>
       </c>
       <c r="F77" t="n">
-        <v>0.3530003613746995</v>
+        <v>0.3530003613746806</v>
       </c>
     </row>
     <row r="78">
@@ -2164,16 +2164,16 @@
         <v>2019</v>
       </c>
       <c r="C79" t="n">
-        <v>75.37646177489179</v>
+        <v>75.37646177489177</v>
       </c>
       <c r="D79" t="n">
         <v>75.53</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1535382251082069</v>
+        <v>0.1535382251082353</v>
       </c>
       <c r="F79" t="n">
-        <v>0.2032811136081119</v>
+        <v>0.2032811136081495</v>
       </c>
     </row>
     <row r="80">
@@ -2186,16 +2186,16 @@
         <v>2019</v>
       </c>
       <c r="C80" t="n">
-        <v>73.03653798199352</v>
+        <v>73.0365379819935</v>
       </c>
       <c r="D80" t="n">
         <v>73.34</v>
       </c>
       <c r="E80" t="n">
-        <v>0.3034620180064849</v>
+        <v>0.3034620180064991</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4137742268973069</v>
+        <v>0.4137742268973263</v>
       </c>
     </row>
     <row r="81">
@@ -2208,16 +2208,16 @@
         <v>2019</v>
       </c>
       <c r="C81" t="n">
-        <v>63.5259384325397</v>
+        <v>63.52593843253967</v>
       </c>
       <c r="D81" t="n">
         <v>67.26000000000001</v>
       </c>
       <c r="E81" t="n">
-        <v>3.734061567460309</v>
+        <v>3.734061567460337</v>
       </c>
       <c r="F81" t="n">
-        <v>5.55168237802603</v>
+        <v>5.551682378026073</v>
       </c>
     </row>
     <row r="82">
@@ -2230,16 +2230,16 @@
         <v>2019</v>
       </c>
       <c r="C82" t="n">
-        <v>74.56792947871575</v>
+        <v>74.56792947871577</v>
       </c>
       <c r="D82" t="n">
         <v>74.20999999999999</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.3579294787157608</v>
+        <v>-0.357929478715775</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.4823197395442134</v>
+        <v>-0.4823197395442326</v>
       </c>
     </row>
     <row r="83">
@@ -2252,16 +2252,16 @@
         <v>2019</v>
       </c>
       <c r="C83" t="n">
-        <v>72.32609638089581</v>
+        <v>72.32609638089582</v>
       </c>
       <c r="D83" t="n">
         <v>72.73999999999999</v>
       </c>
       <c r="E83" t="n">
-        <v>0.4139036191041896</v>
+        <v>0.4139036191041754</v>
       </c>
       <c r="F83" t="n">
-        <v>0.5690178981360869</v>
+        <v>0.5690178981360674</v>
       </c>
     </row>
     <row r="84">
@@ -2274,16 +2274,16 @@
         <v>2019</v>
       </c>
       <c r="C84" t="n">
-        <v>77.85222816919192</v>
+        <v>77.85222816919193</v>
       </c>
       <c r="D84" t="n">
         <v>78.08</v>
       </c>
       <c r="E84" t="n">
-        <v>0.2277718308080807</v>
+        <v>0.2277718308080665</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2917159718341197</v>
+        <v>0.2917159718341016</v>
       </c>
     </row>
     <row r="85">
@@ -2296,16 +2296,16 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>76.27355636363635</v>
+        <v>76.27355636363633</v>
       </c>
       <c r="D85" t="n">
         <v>76.38</v>
       </c>
       <c r="E85" t="n">
-        <v>0.1064436363636503</v>
+        <v>0.1064436363636645</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1393606132019511</v>
+        <v>0.1393606132019698</v>
       </c>
     </row>
     <row r="86">
